--- a/all_hits_drugs.xlsx
+++ b/all_hits_drugs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legit\Documents\UCSF\clinicalcandidates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4817860-7CA0-4781-9A67-CCE8E91151E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76291E62-9523-4CDB-B0A7-E33E1E924554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{654B6AD4-6A08-4AE1-99D4-78E97C786646}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="1164">
   <si>
     <t>paper</t>
   </si>
@@ -3518,7 +3518,13 @@
     <t>Retrieved</t>
   </si>
   <si>
-    <t>Dropped</t>
+    <t>DOI_present_regex_1</t>
+  </si>
+  <si>
+    <t>Regex dropped</t>
+  </si>
+  <si>
+    <t>Pairing dropped</t>
   </si>
 </sst>
 </file>
@@ -4380,7 +4386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAE3336-7233-4D93-8017-452EE45ABAC8}">
-  <dimension ref="A1:R223"/>
+  <dimension ref="A1:T223"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -4393,9 +4399,10 @@
     <col min="12" max="12" width="11.6640625" customWidth="1"/>
     <col min="13" max="13" width="52.21875" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="17" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4442,16 +4449,22 @@
         <v>1158</v>
       </c>
       <c r="P1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Q1" t="s">
         <v>1159</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1160</v>
       </c>
-      <c r="R1" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4495,18 +4508,25 @@
         <v>0</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <f>IF(O2,1,0)</f>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
       </c>
       <c r="R2">
+        <f>IF(Q2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <f>IF(AND(Q2,NOT(P2)),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T2">
         <f>IF(AND(P2,NOT(O2)),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4552,16 +4572,23 @@
       <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3">
-        <f>IF(O3,1,0)</f>
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R66" si="0">IF(AND(P3,NOT(O3)),1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <f t="shared" ref="R3:R66" si="0">IF(Q3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S66" si="1">IF(AND(Q3,NOT(P3)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T66" si="2">IF(AND(P3,NOT(O3)),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4607,16 +4634,23 @@
       <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4">
-        <f t="shared" ref="Q4:Q67" si="1">IF(O4,1,0)</f>
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4662,16 +4696,23 @@
       <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5">
-        <f t="shared" si="1"/>
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -4717,16 +4758,23 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4772,16 +4820,23 @@
       <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <f t="shared" si="1"/>
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -4825,18 +4880,25 @@
         <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
       </c>
       <c r="R8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4880,18 +4942,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
       </c>
       <c r="R9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4932,18 +5001,25 @@
         <v>0</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -4987,18 +5063,25 @@
         <v>0</v>
       </c>
       <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
       </c>
       <c r="R11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -5042,18 +5125,25 @@
         <v>0</v>
       </c>
       <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
       </c>
       <c r="R12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -5099,16 +5189,23 @@
       <c r="P13" t="b">
         <v>1</v>
       </c>
-      <c r="Q13">
-        <f t="shared" si="1"/>
+      <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -5154,16 +5251,23 @@
       <c r="P14" t="b">
         <v>1</v>
       </c>
-      <c r="Q14">
-        <f t="shared" si="1"/>
+      <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -5209,16 +5313,23 @@
       <c r="P15" t="b">
         <v>1</v>
       </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q15" t="b">
+        <v>1</v>
       </c>
       <c r="R15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -5262,18 +5373,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
       </c>
       <c r="R16">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -5317,18 +5435,25 @@
         <v>0</v>
       </c>
       <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
       </c>
       <c r="R17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -5372,18 +5497,25 @@
         <v>0</v>
       </c>
       <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
       </c>
       <c r="R18">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -5427,18 +5559,25 @@
         <v>0</v>
       </c>
       <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
       </c>
       <c r="R19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -5482,18 +5621,25 @@
         <v>0</v>
       </c>
       <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
       </c>
       <c r="R20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -5537,18 +5683,25 @@
         <v>1</v>
       </c>
       <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -5592,18 +5745,25 @@
         <v>0</v>
       </c>
       <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
       </c>
       <c r="R22">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S22">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -5647,18 +5807,25 @@
         <v>1</v>
       </c>
       <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -5702,18 +5869,25 @@
         <v>1</v>
       </c>
       <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -5759,16 +5933,23 @@
       <c r="P25" t="b">
         <v>1</v>
       </c>
-      <c r="Q25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q25" t="b">
+        <v>1</v>
       </c>
       <c r="R25">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -5812,18 +5993,25 @@
         <v>0</v>
       </c>
       <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
       </c>
       <c r="R26">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -5864,18 +6052,25 @@
         <v>0</v>
       </c>
       <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
       </c>
       <c r="R27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -5921,16 +6116,23 @@
       <c r="P28" t="b">
         <v>0</v>
       </c>
-      <c r="Q28">
-        <f t="shared" si="1"/>
+      <c r="Q28" t="b">
         <v>0</v>
       </c>
       <c r="R28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -5976,16 +6178,23 @@
       <c r="P29" t="b">
         <v>0</v>
       </c>
-      <c r="Q29">
-        <f t="shared" si="1"/>
+      <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -6031,16 +6240,23 @@
       <c r="P30" t="b">
         <v>1</v>
       </c>
-      <c r="Q30">
-        <f t="shared" si="1"/>
+      <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -6084,18 +6300,25 @@
         <v>0</v>
       </c>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
       </c>
       <c r="R31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S31">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -6139,18 +6362,25 @@
         <v>0</v>
       </c>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
       </c>
       <c r="R32">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -6196,16 +6426,23 @@
       <c r="P33" t="b">
         <v>1</v>
       </c>
-      <c r="Q33">
-        <f t="shared" si="1"/>
+      <c r="Q33" t="b">
         <v>1</v>
       </c>
       <c r="R33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -6249,18 +6486,25 @@
         <v>0</v>
       </c>
       <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
       </c>
       <c r="R34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S34">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -6301,18 +6545,25 @@
         <v>0</v>
       </c>
       <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
       </c>
       <c r="R35">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -6355,16 +6606,23 @@
       <c r="P36" t="b">
         <v>1</v>
       </c>
-      <c r="Q36">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q36" t="b">
+        <v>1</v>
       </c>
       <c r="R36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -6405,18 +6663,25 @@
         <v>0</v>
       </c>
       <c r="P37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
       </c>
       <c r="R37">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S37">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -6462,16 +6727,23 @@
       <c r="P38" t="b">
         <v>1</v>
       </c>
-      <c r="Q38">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q38" t="b">
+        <v>1</v>
       </c>
       <c r="R38">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6517,16 +6789,23 @@
       <c r="P39" t="b">
         <v>1</v>
       </c>
-      <c r="Q39">
-        <f t="shared" si="1"/>
+      <c r="Q39" t="b">
         <v>1</v>
       </c>
       <c r="R39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -6572,16 +6851,23 @@
       <c r="P40" t="b">
         <v>1</v>
       </c>
-      <c r="Q40">
-        <f t="shared" si="1"/>
+      <c r="Q40" t="b">
         <v>1</v>
       </c>
       <c r="R40">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -6625,18 +6911,25 @@
         <v>0</v>
       </c>
       <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
       </c>
       <c r="R41">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S41">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -6680,18 +6973,25 @@
         <v>0</v>
       </c>
       <c r="P42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>1</v>
       </c>
       <c r="R42">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -6737,16 +7037,23 @@
       <c r="P43" t="b">
         <v>0</v>
       </c>
-      <c r="Q43">
-        <f t="shared" si="1"/>
+      <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -6790,18 +7097,25 @@
         <v>0</v>
       </c>
       <c r="P44" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>1</v>
       </c>
       <c r="R44">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -6847,16 +7161,23 @@
       <c r="P45" t="b">
         <v>1</v>
       </c>
-      <c r="Q45">
-        <f t="shared" si="1"/>
+      <c r="Q45" t="b">
         <v>1</v>
       </c>
       <c r="R45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -6900,18 +7221,25 @@
         <v>0</v>
       </c>
       <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
       </c>
       <c r="R46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S46">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -6955,18 +7283,25 @@
         <v>0</v>
       </c>
       <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>1</v>
       </c>
       <c r="R47">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -7012,16 +7347,23 @@
       <c r="P48" t="b">
         <v>1</v>
       </c>
-      <c r="Q48">
-        <f t="shared" si="1"/>
+      <c r="Q48" t="b">
         <v>1</v>
       </c>
       <c r="R48">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -7067,16 +7409,23 @@
       <c r="P49" t="b">
         <v>1</v>
       </c>
-      <c r="Q49">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q49" t="b">
+        <v>1</v>
       </c>
       <c r="R49">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S49">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -7122,16 +7471,23 @@
       <c r="P50" t="b">
         <v>0</v>
       </c>
-      <c r="Q50">
-        <f t="shared" si="1"/>
+      <c r="Q50" t="b">
         <v>0</v>
       </c>
       <c r="R50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -7174,16 +7530,23 @@
       <c r="P51" t="b">
         <v>0</v>
       </c>
-      <c r="Q51">
-        <f t="shared" si="1"/>
+      <c r="Q51" t="b">
         <v>0</v>
       </c>
       <c r="R51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -7229,16 +7592,23 @@
       <c r="P52" t="b">
         <v>1</v>
       </c>
-      <c r="Q52">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="Q52" t="b">
+        <v>1</v>
       </c>
       <c r="R52">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -7282,18 +7652,25 @@
         <v>0</v>
       </c>
       <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>1</v>
       </c>
       <c r="R53">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S53">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -7337,18 +7714,25 @@
         <v>0</v>
       </c>
       <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>1</v>
       </c>
       <c r="R54">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -7392,18 +7776,25 @@
         <v>0</v>
       </c>
       <c r="P55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>1</v>
       </c>
       <c r="R55">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S55">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -7444,18 +7835,25 @@
         <v>1</v>
       </c>
       <c r="P56" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" t="b">
         <v>1</v>
       </c>
       <c r="R56">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -7499,18 +7897,25 @@
         <v>0</v>
       </c>
       <c r="P57" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q57">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>1</v>
       </c>
       <c r="R57">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -7554,18 +7959,25 @@
         <v>0</v>
       </c>
       <c r="P58" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q58">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>1</v>
       </c>
       <c r="R58">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S58">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -7606,18 +8018,25 @@
         <v>0</v>
       </c>
       <c r="P59" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q59">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>1</v>
       </c>
       <c r="R59">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S59">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -7661,18 +8080,25 @@
         <v>0</v>
       </c>
       <c r="P60" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>1</v>
       </c>
       <c r="R60">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S60">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -7716,18 +8142,25 @@
         <v>0</v>
       </c>
       <c r="P61" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q61">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>1</v>
       </c>
       <c r="R61">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S61">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -7768,18 +8201,25 @@
         <v>0</v>
       </c>
       <c r="P62" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q62">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q62" t="b">
+        <v>1</v>
       </c>
       <c r="R62">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S62">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -7822,16 +8262,23 @@
       <c r="P63" t="b">
         <v>1</v>
       </c>
-      <c r="Q63">
-        <f t="shared" si="1"/>
+      <c r="Q63" t="b">
         <v>1</v>
       </c>
       <c r="R63">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -7877,16 +8324,23 @@
       <c r="P64" t="b">
         <v>1</v>
       </c>
-      <c r="Q64">
-        <f t="shared" si="1"/>
+      <c r="Q64" t="b">
         <v>1</v>
       </c>
       <c r="R64">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -7930,18 +8384,25 @@
         <v>0</v>
       </c>
       <c r="P65" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q65">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
       </c>
       <c r="R65">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -7987,16 +8448,23 @@
       <c r="P66" t="b">
         <v>1</v>
       </c>
-      <c r="Q66">
-        <f t="shared" si="1"/>
+      <c r="Q66" t="b">
         <v>1</v>
       </c>
       <c r="R66">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -8040,18 +8508,25 @@
         <v>0</v>
       </c>
       <c r="P67" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q67">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
       </c>
       <c r="R67">
-        <f t="shared" ref="R67" si="2">IF(AND(P67,NOT(O67)),1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+        <f t="shared" ref="R67:R68" si="3">IF(Q67,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <f t="shared" ref="S67:S68" si="4">IF(AND(Q67,NOT(P67)),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <f t="shared" ref="T67:T130" si="5">IF(AND(P67,NOT(O67)),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>522</v>
       </c>
@@ -8073,16 +8548,20 @@
       <c r="N68" t="s">
         <v>523</v>
       </c>
-      <c r="Q68">
-        <f>SUM(Q2:Q67)</f>
-        <v>20</v>
-      </c>
       <c r="R68">
         <f>SUM(R2:R67)</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+      <c r="S68">
+        <f t="shared" ref="S68:T68" si="6">SUM(S2:S67)</f>
+        <v>39</v>
+      </c>
+      <c r="T68">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>522</v>
       </c>
@@ -8105,7 +8584,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>522</v>
       </c>
@@ -8128,7 +8607,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>522</v>
       </c>
@@ -8151,7 +8630,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>522</v>
       </c>
@@ -8174,7 +8653,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>522</v>
       </c>
@@ -8197,7 +8676,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>522</v>
       </c>
@@ -8220,7 +8699,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>522</v>
       </c>
@@ -8243,7 +8722,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>522</v>
       </c>
@@ -8266,7 +8745,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>522</v>
       </c>
@@ -8289,7 +8768,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>522</v>
       </c>
@@ -8312,7 +8791,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>522</v>
       </c>
@@ -8335,7 +8814,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>522</v>
       </c>
